--- a/scripts/output/scholar_6089491.xlsx
+++ b/scripts/output/scholar_6089491.xlsx
@@ -474,22 +474,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
+          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
+          <t>SO Devi, AC Irawati</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -548,22 +548,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
+          <t>Optimasi Pemulihan Hak Korban Dalam Kasus Perundungan: Analisis Implementasi Pasal 9 Ayat (1a) Undang-Undang Perlindungan Anak</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Optimasi Pemulihan Hak Korban Dalam Kasus Perundungan: Analisis Implementasi Pasal 9 Ayat (1a) Undang-Undang Perlindungan Anak'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>W Winarti, AC Irawati</t>
+          <t>PM Sipahutar, AC Irawati</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 77-86, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
+          <t>Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SO Devi, AC Irawati</t>
+          <t>AK Devi, I Yuliawan, AC Irawati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 234-241, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
+          <t>Pejabat Desa Indonesia Dalam Upaya Mencari Kejelasan Hukum Mengenai Status Pekerjaan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Pejabat Desa Indonesia Dalam Upaya Mencari Kejelasan Hukum Mengenai Status Pekerjaan'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AC Irawati</t>
+          <t>T Triyono, AC Irawati</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 124-131, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -696,22 +696,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.</t>
+          <t>Penipuan Berbasis Online Di Kota Semarang: Analisis Yuridis-Normatif Dalam Perspektif Hukum Pidana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penipuan Berbasis Online Di Kota Semarang: Analisis Yuridis-Normatif Dalam Perspektif Hukum Pidana'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S Sonhaji, AC Irawati</t>
+          <t>TD Satria, H Irhamdesstya, AC Irawati</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 242-250, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 251-259, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -733,22 +733,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Urgensi Kesadaran Digital dalam Mewujudkan Ruang Aman melalui Literasi Digital dan Penerapan Proporsional Undang-Undang ITE</t>
+          <t>Pendekatan Hukum Terhadap Pembangunan Teknologi Informasi Dan Perlindungan Data Pribadi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Urgensi Kesadaran Digital dalam Mewujudkan Ruang Aman melalui Literasi Digital dan Penerapan Proporsional Undang-Undang ITE'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Pendekatan Hukum Terhadap Pembangunan Teknologi Informasi Dan Perlindungan Data Pribadi'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F Budiarti, H Irhamdesetya, AC Irawati</t>
+          <t>G Aulia, AC Irawati</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 142-151, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 115-123, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -770,22 +770,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti</t>
+          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>QM Ulfa, AC Irawati</t>
+          <t>AC Irawati</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5827-5832, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -807,22 +807,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr</t>
+          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SO Devi, AC Irawati</t>
+          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5566-5573, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">

--- a/scripts/output/scholar_6089491.xlsx
+++ b/scripts/output/scholar_6089491.xlsx
@@ -474,22 +474,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
+          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SO Devi, AC Irawati</t>
+          <t>QM Ulfa, AC Irawati</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5827-5832, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik</t>
+          <t>Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KA Saputra, M Lativ, AC Irawati</t>
+          <t>AK Devi, I Yuliawan, AC Irawati</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 227-233, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 234-241, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,22 +548,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optimasi Pemulihan Hak Korban Dalam Kasus Perundungan: Analisis Implementasi Pasal 9 Ayat (1a) Undang-Undang Perlindungan Anak</t>
+          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Optimasi Pemulihan Hak Korban Dalam Kasus Perundungan: Analisis Implementasi Pasal 9 Ayat (1a) Undang-Undang Perlindungan Anak'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PM Sipahutar, AC Irawati</t>
+          <t>W Winarti, AC Irawati</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 77-86, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang</t>
+          <t>Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AK Devi, I Yuliawan, AC Irawati</t>
+          <t>S Sholehuddin, AC Irawati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 234-241, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 291-299, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pejabat Desa Indonesia Dalam Upaya Mencari Kejelasan Hukum Mengenai Status Pekerjaan</t>
+          <t>Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Pejabat Desa Indonesia Dalam Upaya Mencari Kejelasan Hukum Mengenai Status Pekerjaan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T Triyono, AC Irawati</t>
+          <t>S Sholehuddin, AC Irawati</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 124-131, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 291-299, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances</t>
+          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>W Waryadi, AC Irawati</t>
+          <t>HN Hanifah, AC Irawati</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNTAG Law Review 9 (2), 82-92, 2026</t>
+          <t>Jurnal Pengabdian Masyarakat dan Riset Pendidikan 4 (3), 20402-20404, 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -696,22 +696,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Penipuan Berbasis Online Di Kota Semarang: Analisis Yuridis-Normatif Dalam Perspektif Hukum Pidana</t>
+          <t>PERLINDUNGAN DATA PRIBADI SEBAGAI INSTRUMEN HUKUM DALAM MENANGGULANGI KEJAHATAN PERBANKAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penipuan Berbasis Online Di Kota Semarang: Analisis Yuridis-Normatif Dalam Perspektif Hukum Pidana'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'PERLINDUNGAN DATA PRIBADI SEBAGAI INSTRUMEN HUKUM DALAM MENANGGULANGI KEJAHATAN PERBANKAN'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TD Satria, H Irhamdesstya, AC Irawati</t>
+          <t>N Sugiarto, I Yuliawan, AC Irawati</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 251-259, 2026</t>
+          <t>Pendas: Jurnal Ilmiah Pendidikan Dasar 11 (01), 260-275, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pendekatan Hukum Terhadap Pembangunan Teknologi Informasi Dan Perlindungan Data Pribadi</t>
+          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Pendekatan Hukum Terhadap Pembangunan Teknologi Informasi Dan Perlindungan Data Pribadi'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>G Aulia, AC Irawati</t>
+          <t>HN Hanifah, AC Irawati</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 115-123, 2026</t>
+          <t>Jurnal Pengabdian Masyarakat dan Riset Pendidikan 4 (3), 20402-20404, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
+          <t>Penerapan Undang-Undang Tentang Informasi Dan Transaksi Elektronik (Uu Ite) Dalam Kebebasan Berpendapat Dan Berekspresi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Undang-Undang Tentang Informasi Dan Transaksi Elektronik (Uu Ite) Dalam Kebebasan Berpendapat Dan Berekspresi'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AC Irawati</t>
+          <t>H Sinaga, AC Irawati</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 172-180, 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -807,22 +807,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
+          <t>Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
+          <t>A Wijayanto, AC Irawati</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 68-76, 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">

--- a/scripts/output/scholar_6089491.xlsx
+++ b/scripts/output/scholar_6089491.xlsx
@@ -474,22 +474,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti</t>
+          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QM Ulfa, AC Irawati</t>
+          <t>SO Devi, AC Irawati</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5827-5832, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang</t>
+          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Penegakan Peraturan Daerah (Perda) Ketentraman Masyarakat Dan Perlindungan Masyarakat Di Kabupaten Semarang'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AK Devi, I Yuliawan, AC Irawati</t>
+          <t>AC Irawati</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 234-241, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,22 +548,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
+          <t>Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>W Winarti, AC Irawati</t>
+          <t>W Waryadi, AC Irawati</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
+          <t>UNTAG Law Review 9 (2), 82-92, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi</t>
+          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S Sholehuddin, AC Irawati</t>
+          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 291-299, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi</t>
+          <t>Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Dominasi Kepentingan Partai Politik Dalam Proses Legislasi Di Dpr: Sebuah Studi Hukum Konstitusi'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S Sholehuddin, AC Irawati</t>
+          <t>KA Saputra, M Lativ, AC Irawati</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 291-299, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 227-233, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif</t>
+          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HN Hanifah, AC Irawati</t>
+          <t>W Winarti, AC Irawati</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jurnal Pengabdian Masyarakat dan Riset Pendidikan 4 (3), 20402-20404, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -696,22 +696,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PERLINDUNGAN DATA PRIBADI SEBAGAI INSTRUMEN HUKUM DALAM MENANGGULANGI KEJAHATAN PERBANKAN</t>
+          <t>Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'PERLINDUNGAN DATA PRIBADI SEBAGAI INSTRUMEN HUKUM DALAM MENANGGULANGI KEJAHATAN PERBANKAN'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N Sugiarto, I Yuliawan, AC Irawati</t>
+          <t>SO Devi, AC Irawati</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pendas: Jurnal Ilmiah Pendidikan Dasar 11 (01), 260-275, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5566-5573, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif</t>
+          <t>Model Pencegahan Penarikan Kendaraan Leasing Melalui Komunikasi Proaktif Di Kota Semarang</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Ditinjau Dari Asas Keadilan Retributif'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Model Pencegahan Penarikan Kendaraan Leasing Melalui Komunikasi Proaktif Di Kota Semarang'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HN Hanifah, AC Irawati</t>
+          <t>RD Saputra, H Irhamdesstya, AC Irawati</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jurnal Pengabdian Masyarakat dan Riset Pendidikan 4 (3), 20402-20404, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 216-226, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penerapan Undang-Undang Tentang Informasi Dan Transaksi Elektronik (Uu Ite) Dalam Kebebasan Berpendapat Dan Berekspresi</t>
+          <t>Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Undang-Undang Tentang Informasi Dan Transaksi Elektronik (Uu Ite) Dalam Kebebasan Berpendapat Dan Berekspresi'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>H Sinaga, AC Irawati</t>
+          <t>A Wijayanto, AC Irawati</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 172-180, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 68-76, 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -807,22 +807,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang</t>
+          <t>Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A Wijayanto, AC Irawati</t>
+          <t>S Sonhaji, AC Irawati</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 68-76, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 242-250, 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">

--- a/scripts/output/scholar_6089491.xlsx
+++ b/scripts/output/scholar_6089491.xlsx
@@ -474,22 +474,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
+          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SO Devi, AC Irawati</t>
+          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
+          <t>Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik'</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AC Irawati</t>
+          <t>KA Saputra, M Lativ, AC Irawati</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 227-233, 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,22 +548,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances</t>
+          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>W Waryadi, AC Irawati</t>
+          <t>W Winarti, AC Irawati</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UNTAG Law Review 9 (2), 82-92, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta</t>
+          <t>Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Peran Ahli Patologi Klinis Dalam Memerangi Perdagangan Ilegal Obat Resep Terbatas Di Kabupaten Sleman, Daerah Istimewa Yogyakarta'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindak Pidana Perjudian Melalui Transaksi Informasi dan Elektronik: Studi Putusan Nomor 7104/K/Pid. Sus/2025'</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AS Sanggacita, H Irhamdessetya, AC Irawati</t>
+          <t>SO Devi, AC Irawati</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 283-290, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5574-5580, 2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -622,22 +622,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik</t>
+          <t>Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Penerapan Demokrasi Partisipatif Untuk Memperkuat Tata Kelola Desa Yang Baik'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penegakan Hukum Tindakan Kriminal Yang Dilakukan Dalam Perjudian Online Oleh Anak-Anak (Studi Kasus Di Kepolisian Metropolitan Semarang)'</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KA Saputra, M Lativ, AC Irawati</t>
+          <t>AC Irawati</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 227-233, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 181-190, 2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan</t>
+          <t>Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Keadilan Restoratif: Model Perlindungan Hukum Oleh Aparat Penegak Hukum (Polisi) Dalam Menangani Anak-Anak Yang Terlibat Dalam Perundungan'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Criminal Responsibility of Business Actors for The Distribution of Food Containing Dangerous Substances'</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>W Winarti, AC Irawati</t>
+          <t>W Waryadi, AC Irawati</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 105-114, 2026</t>
+          <t>UNTAG Law Review 9 (2), 82-92, 2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -696,22 +696,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr</t>
+          <t>Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.'</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SO Devi, AC Irawati</t>
+          <t>S Sonhaji, AC Irawati</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5566-5573, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 242-250, 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -733,22 +733,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Model Pencegahan Penarikan Kendaraan Leasing Melalui Komunikasi Proaktif Di Kota Semarang</t>
+          <t>Urgensi Kesadaran Digital dalam Mewujudkan Ruang Aman melalui Literasi Digital dan Penerapan Proporsional Undang-Undang ITE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Model Pencegahan Penarikan Kendaraan Leasing Melalui Komunikasi Proaktif Di Kota Semarang'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Urgensi Kesadaran Digital dalam Mewujudkan Ruang Aman melalui Literasi Digital dan Penerapan Proporsional Undang-Undang ITE'</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RD Saputra, H Irhamdesstya, AC Irawati</t>
+          <t>F Budiarti, H Irhamdesetya, AC Irawati</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 216-226, 2026</t>
+          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 142-151, 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -770,22 +770,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang</t>
+          <t>Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi E-Faktur Pajak Kendaraan Bermotor dalam Perspektif Hukum Administrasi Negara pada Polrestabes Semarang'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Penjatuhan Pidana Dalam Tindak Pidana Kekerasan Dalam Rumah Tangga Mewujudkan Kepastian Hukum: Studi Putusan Nomor 121/Pid. Sus/2025/PN Pti'</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A Wijayanto, AC Irawati</t>
+          <t>QM Ulfa, AC Irawati</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 68-76, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5827-5832, 2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -807,22 +807,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.</t>
+          <t>Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/scholar?q=+intitle:'Implementasi Ketentuan Batas Usia Dewasa dalam Pelayanan Hukum dan Administrasi Kependudukan pada Pemerintah Desa Mejagong, Kecamatan Randudongkal, Kabupaten Pemalang.'</t>
+          <t>https://scholar.google.com/scholar?q=+intitle:'Model Penegakan Hukum Pada Tindak Pidana Pencurian Anak Melalui Diversi: Studi Putusan Nomor 7/Pid. Sus-Anak/2025/PN Unr'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S Sonhaji, AC Irawati</t>
+          <t>SO Devi, AC Irawati</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Iuris Studia: Jurnal Kajian Hukum 7 (1), 242-250, 2026</t>
+          <t>Al-Zayn: Jurnal Ilmu Sosial &amp; Hukum 4 (1), 5566-5573, 2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
